--- a/01-dcf-valuation/Sonatel_DCF_Model.xlsx
+++ b/01-dcf-valuation/Sonatel_DCF_Model.xlsx
@@ -20,7 +20,7 @@
     <definedName function="false" hidden="false" localSheetId="5" name="_xlnm.Print_Area" vbProcedure="false">Checks!$A$1:$E$17</definedName>
     <definedName function="false" hidden="false" localSheetId="4" name="_xlnm.Print_Area" vbProcedure="false">Comps!$A$1:$F$12</definedName>
     <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">Cover!$A$1:$K$16</definedName>
-    <definedName function="false" hidden="false" localSheetId="2" name="_xlnm.Print_Area" vbProcedure="false">DCF!$A$1:$S$40</definedName>
+    <definedName function="false" hidden="false" localSheetId="2" name="_xlnm.Print_Area" vbProcedure="false">DCF!$A$1:$S$41</definedName>
     <definedName function="false" hidden="false" localSheetId="3" name="_xlnm.Print_Area" vbProcedure="false">Sensitivity!$A$1:$F$14</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
@@ -32,8 +32,88 @@
 </workbook>
 </file>
 
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <authors>
+    <author>Unknown Author</author>
+  </authors>
+  <commentList>
+    <comment ref="E23" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">WACC fixé en valeur unique (hypothèse personnelle), faute de données fiables à cette maille (bêta coté, dette nette consolidée, spread souverain Sénégal sur émission internationale) pour construire un CAPM complet comparable à celui de Danone. Le niveau retenu, supérieur à un WACC de marché développé, est cohérent avec le cadre théorique proposé pour les marchés émergents (taux obligataire de référence + spread souverain + bêta sectoriel x prime de risque actions), décrit par Vernimmen (Corporate Finance, chapitre sur le coût du capital en marché émergent).</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <authors>
+    <author>Unknown Author</author>
+  </authors>
+  <commentList>
+    <comment ref="B10" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Convention mid-year : les flux sont supposés perçus en moyenne au milieu de chaque exercice (période n-0,5), plutôt qu'en toute fin d'année. Convention standard en modélisation DCF (guide BIWS, Breaking Into Wall Street). La valeur terminale (Gordon growth) est actualisée avec le même facteur que le dernier flux explicite (année 5), sans ajout supplémentaire de 0,5, conformément à cette méthode.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B33" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Hypothèse : maintenue constante jusqu'en 2030, cf. onglet Assumptions.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B35" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Multiple de sortie implicite = valeur terminale / EBITDAaL implicite de l'année 5 (2030).</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B36" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Multiple de référence : comparable coté Maroc Telecom, cf. onglet Comps.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="92">
   <si>
     <t xml:space="preserve">Groupe Sonatel (BRVM : SNTS) - Modèle DCF et comparables</t>
   </si>
@@ -167,7 +247,7 @@
     <t xml:space="preserve">Free cash-flow (FCFF proxy)</t>
   </si>
   <si>
-    <t xml:space="preserve">Période d'actualisation (n)</t>
+    <t xml:space="preserve">Période d'actualisation (n, convention mid-year)</t>
   </si>
   <si>
     <t xml:space="preserve">Facteur d'actualisation</t>
@@ -194,7 +274,7 @@
     <t xml:space="preserve">VE implicite (DCF)</t>
   </si>
   <si>
-    <t xml:space="preserve">Cours de marché, pour mémoire</t>
+    <t xml:space="preserve">Cours de marché</t>
   </si>
   <si>
     <t xml:space="preserve">VE implicite par action (FCFA)</t>
@@ -206,6 +286,24 @@
     <t xml:space="preserve">Lecture : la dette nette de Sonatel n'est pas publiée à une maille fiable (voir Assumptions/Cover). Les deux lignes ci-dessus comparent donc une VE implicite du DCF à un cours de marché (capitalisation), et non une valeur des fonds propres à une valeur des fonds propres : aucune conclusion de potentiel de hausse ou de baisse n'en est tirée.</t>
   </si>
   <si>
+    <t xml:space="preserve">RECOUPEMENT DE LA VALEUR TERMINALE (MULTIPLE DE SORTIE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marge d'EBITDAaL (hypothèse de projection)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EBITDAaL implicite, année 5 (2030, Md FCFA)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multiple de sortie implicite (VT / EBITDAaL an 5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comparable Maroc Telecom (pour mémoire)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lecture : ce recoupement applique la méthode des multiples de sortie en complément de la méthode Gordon growth (cf. guide BIWS, Key Rule #4) : on reconvertit la valeur terminale obtenue par Gordon growth en un multiple implicite VE/EBITDAaL à l'année 5, à comparer avec le comparable régional déjà retenu (onglet Comps, Maroc Telecom). La marge d'EBITDAaL à l'année 5 reprend l'hypothèse de marge constante déjà utilisée pour le free cash-flow dans l'onglet Assumptions.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Sensibilité - VE implicite par action (FCFA, indicatif)</t>
   </si>
   <si>
@@ -285,6 +383,9 @@
   </si>
   <si>
     <t xml:space="preserve">Synthèse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multiple de sortie implicite (VT) du même ordre de grandeur que le comparable régional</t>
   </si>
   <si>
     <t xml:space="preserve">Note : ces contrôles vérifient la cohérence interne du modèle (pas d'erreur de construction), pas la justesse des hypothèses elles-mêmes.</t>
@@ -294,18 +395,19 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="9">
+  <numFmts count="10">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0.0;\(#,##0.0\);\-"/>
     <numFmt numFmtId="166" formatCode="#,##0;\(#,##0\);\-"/>
     <numFmt numFmtId="167" formatCode="0.0%;\(0.0%\);\-"/>
     <numFmt numFmtId="168" formatCode="0"/>
-    <numFmt numFmtId="169" formatCode="0.000"/>
-    <numFmt numFmtId="170" formatCode="#,##0&quot; FCFA&quot;"/>
-    <numFmt numFmtId="171" formatCode="#,##0"/>
+    <numFmt numFmtId="169" formatCode="0.0"/>
+    <numFmt numFmtId="170" formatCode="0.000"/>
+    <numFmt numFmtId="171" formatCode="#,##0&quot; FCFA&quot;"/>
     <numFmt numFmtId="172" formatCode="0.00\x;\(0.00&quot;x)&quot;;\-"/>
+    <numFmt numFmtId="173" formatCode="#,##0"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -370,6 +472,11 @@
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b val="true"/>
@@ -494,7 +601,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="34">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -551,7 +658,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -563,23 +670,23 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="169" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="170" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="true"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -587,23 +694,27 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="172" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="172" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -615,7 +726,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -623,7 +734,7 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -879,11 +990,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="50648925"/>
-        <c:axId val="91744816"/>
+        <c:axId val="90558761"/>
+        <c:axId val="50465841"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="50648925"/>
+        <c:axId val="90558761"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -914,7 +1025,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="91744816"/>
+        <c:crossAx val="50465841"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -922,7 +1033,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="91744816"/>
+        <c:axId val="50465841"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -997,7 +1108,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="50648925"/>
+        <c:crossAx val="90558761"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1123,7 +1234,7 @@
                   <c:v>VE implicite (DCF)</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Cours de marché, pour mémoire</c:v>
+                  <c:v>Cours de marché</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1135,7 +1246,7 @@
                 <c:formatCode>#,##0" FCFA"</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>60060.5920286662</c:v>
+                  <c:v>63277.7601805374</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>44980</c:v>
@@ -1146,11 +1257,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="41304291"/>
-        <c:axId val="78075433"/>
+        <c:axId val="61581075"/>
+        <c:axId val="69560963"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="41304291"/>
+        <c:axId val="61581075"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1181,7 +1292,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="78075433"/>
+        <c:crossAx val="69560963"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1189,7 +1300,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="78075433"/>
+        <c:axId val="69560963"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1264,7 +1375,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="41304291"/>
+        <c:crossAx val="61581075"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1303,9 +1414,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>252000</xdr:colOff>
+      <xdr:colOff>248040</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>17640</xdr:rowOff>
+      <xdr:rowOff>13680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -1314,7 +1425,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="9046800" y="790560"/>
-        <a:ext cx="6342480" cy="2875320"/>
+        <a:ext cx="6338520" cy="2871360"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -1333,9 +1444,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>252000</xdr:colOff>
+      <xdr:colOff>248040</xdr:colOff>
       <xdr:row>37</xdr:row>
-      <xdr:rowOff>17640</xdr:rowOff>
+      <xdr:rowOff>13680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -1344,7 +1455,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="9046800" y="4219560"/>
-        <a:ext cx="6342480" cy="2875320"/>
+        <a:ext cx="6338520" cy="2871360"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -1885,6 +1996,7 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -1893,7 +2005,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B2:J30"/>
+  <dimension ref="B2:J41"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="46"/>
@@ -2034,19 +2146,19 @@
         <v>44</v>
       </c>
       <c r="C10" s="17" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D10" s="17" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="E10" s="17" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="F10" s="17" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="G10" s="17" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2055,23 +2167,23 @@
       </c>
       <c r="C11" s="18" t="n">
         <f aca="false">1/(1+Assumptions!$E$23)^C10</f>
-        <v>0.900900900900901</v>
+        <v>0.949157995752499</v>
       </c>
       <c r="D11" s="18" t="n">
         <f aca="false">1/(1+Assumptions!$E$23)^D10</f>
-        <v>0.811622433244055</v>
+        <v>0.85509729347072</v>
       </c>
       <c r="E11" s="18" t="n">
         <f aca="false">1/(1+Assumptions!$E$23)^E10</f>
-        <v>0.73119138130095</v>
+        <v>0.770357922045693</v>
       </c>
       <c r="F11" s="18" t="n">
         <f aca="false">1/(1+Assumptions!$E$23)^F10</f>
-        <v>0.658730974145</v>
+        <v>0.694016145987111</v>
       </c>
       <c r="G11" s="18" t="n">
         <f aca="false">1/(1+Assumptions!$E$23)^G10</f>
-        <v>0.593451328058559</v>
+        <v>0.62523977115956</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2080,23 +2192,23 @@
       </c>
       <c r="C12" s="15" t="n">
         <f aca="false">C9*C11</f>
-        <v>406.792792792793</v>
+        <v>428.582801402084</v>
       </c>
       <c r="D12" s="15" t="n">
         <f aca="false">D9*D11</f>
-        <v>388.468793117442</v>
+        <v>409.277269807395</v>
       </c>
       <c r="E12" s="15" t="n">
         <f aca="false">E9*E11</f>
-        <v>367.470479975959</v>
+        <v>387.15417414213</v>
       </c>
       <c r="F12" s="15" t="n">
         <f aca="false">F9*F11</f>
-        <v>345.951938355745</v>
+        <v>364.482983764438</v>
       </c>
       <c r="G12" s="15" t="n">
         <f aca="false">G9*G11</f>
-        <v>324.135149450427</v>
+        <v>341.497570373888</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2105,7 +2217,7 @@
       </c>
       <c r="C14" s="16" t="n">
         <f aca="false">SUM(C12:G12)</f>
-        <v>1832.81915369237</v>
+        <v>1930.99479948993</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2123,7 +2235,7 @@
       </c>
       <c r="C17" s="16" t="n">
         <f aca="false">C16*G11</f>
-        <v>4173.24004917425</v>
+        <v>4396.78121856381</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2132,7 +2244,7 @@
       </c>
       <c r="C19" s="16" t="n">
         <f aca="false">C14+C17</f>
-        <v>6006.05920286662</v>
+        <v>6327.77601805374</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2148,7 +2260,7 @@
       </c>
       <c r="J20" s="20" t="n">
         <f aca="false">C23</f>
-        <v>60060.5920286662</v>
+        <v>63277.7601805374</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2175,7 +2287,7 @@
       </c>
       <c r="C23" s="21" t="n">
         <f aca="false">C19*1000/C22</f>
-        <v>60060.5920286662</v>
+        <v>63277.7601805374</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2229,18 +2341,105 @@
       <c r="G30" s="23"/>
       <c r="H30" s="23"/>
     </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B32" s="24" t="s">
+        <v>57</v>
+      </c>
+      <c r="C32" s="14"/>
+      <c r="D32" s="14"/>
+      <c r="E32" s="14"/>
+      <c r="F32" s="14"/>
+      <c r="G32" s="14"/>
+      <c r="H32" s="14"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B33" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="C33" s="9" t="n">
+        <f aca="false">Assumptions!E13</f>
+        <v>0.479018251780979</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B34" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C34" s="15" t="n">
+        <f aca="false">G7*C33</f>
+        <v>1192.2916461456</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B35" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="C35" s="25" t="n">
+        <f aca="false">C16/C34</f>
+        <v>5.89801346070343</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B36" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C36" s="25" t="n">
+        <f aca="false">Comps!D7</f>
+        <v>4.9</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B38" s="23" t="s">
+        <v>62</v>
+      </c>
+      <c r="C38" s="23"/>
+      <c r="D38" s="23"/>
+      <c r="E38" s="23"/>
+      <c r="F38" s="23"/>
+      <c r="G38" s="23"/>
+      <c r="H38" s="23"/>
+    </row>
+    <row r="39" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B39" s="23"/>
+      <c r="C39" s="23"/>
+      <c r="D39" s="23"/>
+      <c r="E39" s="23"/>
+      <c r="F39" s="23"/>
+      <c r="G39" s="23"/>
+      <c r="H39" s="23"/>
+    </row>
+    <row r="40" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B40" s="23"/>
+      <c r="C40" s="23"/>
+      <c r="D40" s="23"/>
+      <c r="E40" s="23"/>
+      <c r="F40" s="23"/>
+      <c r="G40" s="23"/>
+      <c r="H40" s="23"/>
+    </row>
+    <row r="41" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B41" s="23"/>
+      <c r="C41" s="23"/>
+      <c r="D41" s="23"/>
+      <c r="E41" s="23"/>
+      <c r="F41" s="23"/>
+      <c r="G41" s="23"/>
+      <c r="H41" s="23"/>
+    </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="B27:H30"/>
+    <mergeCell ref="B38:H41"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.25" right="0.25" top="0.4" bottom="0.4" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
-  <drawing r:id="rId1"/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>
 
@@ -2258,28 +2457,28 @@
   <sheetData>
     <row r="2" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="3" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="24" t="s">
-        <v>59</v>
-      </c>
-      <c r="C5" s="25" t="n">
+        <v>65</v>
+      </c>
+      <c r="C5" s="26" t="n">
         <v>0.02</v>
       </c>
-      <c r="D5" s="25" t="n">
+      <c r="D5" s="26" t="n">
         <v>0.025</v>
       </c>
-      <c r="E5" s="25" t="n">
+      <c r="E5" s="26" t="n">
         <v>0.03</v>
       </c>
-      <c r="F5" s="25" t="n">
+      <c r="F5" s="26" t="n">
         <v>0.035</v>
       </c>
     </row>
@@ -2289,19 +2488,19 @@
       </c>
       <c r="C6" s="10" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$C$9:$G$9,1/(1+$B6)^DCF!$C$10:$G$10)+DCF!$G$9*(1+C$5)/($B6-C$5)/(1+$B6)^DCF!$G$10)*1000/DCF!$C$22</f>
-        <v>66251.4231130559</v>
+        <v>69326.9782670004</v>
       </c>
       <c r="D6" s="10" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$C$9:$G$9,1/(1+$B6)^DCF!$C$10:$G$10)+DCF!$G$9*(1+D$5)/($B6-D$5)/(1+$B6)^DCF!$G$10)*1000/DCF!$C$22</f>
-        <v>69869.6454212702</v>
+        <v>73113.1674164576</v>
       </c>
       <c r="E6" s="10" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$C$9:$G$9,1/(1+$B6)^DCF!$C$10:$G$10)+DCF!$G$9*(1+E$5)/($B6-E$5)/(1+$B6)^DCF!$G$10)*1000/DCF!$C$22</f>
-        <v>74044.5173153637</v>
+        <v>77481.8472042929</v>
       </c>
       <c r="F6" s="10" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$C$9:$G$9,1/(1+$B6)^DCF!$C$10:$G$10)+DCF!$G$9*(1+F$5)/($B6-F$5)/(1+$B6)^DCF!$G$10)*1000/DCF!$C$22</f>
-        <v>78915.2011918061</v>
+        <v>82578.6402901007</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2310,19 +2509,19 @@
       </c>
       <c r="C7" s="10" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$C$9:$G$9,1/(1+$B7)^DCF!$C$10:$G$10)+DCF!$G$9*(1+C$5)/($B7-C$5)/(1+$B7)^DCF!$G$10)*1000/DCF!$C$22</f>
-        <v>62055.0302479339</v>
+        <v>65083.8647974995</v>
       </c>
       <c r="D7" s="10" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$C$9:$G$9,1/(1+$B7)^DCF!$C$10:$G$10)+DCF!$G$9*(1+D$5)/($B7-D$5)/(1+$B7)^DCF!$G$10)*1000/DCF!$C$22</f>
-        <v>65163.8034244928</v>
+        <v>68344.3736120285</v>
       </c>
       <c r="E7" s="10" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$C$9:$G$9,1/(1+$B7)^DCF!$C$10:$G$10)+DCF!$G$9*(1+E$5)/($B7-E$5)/(1+$B7)^DCF!$G$10)*1000/DCF!$C$22</f>
-        <v>68716.687054846</v>
+        <v>72070.6694000618</v>
       </c>
       <c r="F7" s="10" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$C$9:$G$9,1/(1+$B7)^DCF!$C$10:$G$10)+DCF!$G$9*(1+F$5)/($B7-F$5)/(1+$B7)^DCF!$G$10)*1000/DCF!$C$22</f>
-        <v>72816.1681667919</v>
+        <v>76370.2414631771</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2331,19 +2530,19 @@
       </c>
       <c r="C8" s="10" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$C$9:$G$9,1/(1+$B8)^DCF!$C$10:$G$10)+DCF!$G$9*(1+C$5)/($B8-C$5)/(1+$B8)^DCF!$G$10)*1000/DCF!$C$22</f>
-        <v>58353.2077080222</v>
+        <v>61340.2968614125</v>
       </c>
       <c r="D8" s="10" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$C$9:$G$9,1/(1+$B8)^DCF!$C$10:$G$10)+DCF!$G$9*(1+D$5)/($B8-D$5)/(1+$B8)^DCF!$G$10)*1000/DCF!$C$22</f>
-        <v>61046.9311286216</v>
+        <v>64171.9114507745</v>
       </c>
       <c r="E8" s="10" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$C$9:$G$9,1/(1+$B8)^DCF!$C$10:$G$10)+DCF!$G$9*(1+E$5)/($B8-E$5)/(1+$B8)^DCF!$G$10)*1000/DCF!$C$22</f>
-        <v>64099.8176719676</v>
+        <v>67381.0746520514</v>
       </c>
       <c r="F8" s="10" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$C$9:$G$9,1/(1+$B8)^DCF!$C$10:$G$10)+DCF!$G$9*(1+F$5)/($B8-F$5)/(1+$B8)^DCF!$G$10)*1000/DCF!$C$22</f>
-        <v>67588.8308643629</v>
+        <v>71048.6897392251</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2352,19 +2551,19 @@
       </c>
       <c r="C9" s="10" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$C$9:$G$9,1/(1+$B9)^DCF!$C$10:$G$10)+DCF!$G$9*(1+C$5)/($B9-C$5)/(1+$B9)^DCF!$G$10)*1000/DCF!$C$22</f>
-        <v>55063.5084746388</v>
+        <v>58013.0059706066</v>
       </c>
       <c r="D9" s="10" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$C$9:$G$9,1/(1+$B9)^DCF!$C$10:$G$10)+DCF!$G$9*(1+D$5)/($B9-D$5)/(1+$B9)^DCF!$G$10)*1000/DCF!$C$22</f>
-        <v>57415.0772059458</v>
-      </c>
-      <c r="E9" s="26" t="n">
+        <v>60490.5373635152</v>
+      </c>
+      <c r="E9" s="27" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$C$9:$G$9,1/(1+$B9)^DCF!$C$10:$G$10)+DCF!$G$9*(1+E$5)/($B9-E$5)/(1+$B9)^DCF!$G$10)*1000/DCF!$C$22</f>
-        <v>60060.5920286662</v>
+        <v>63277.7601805374</v>
       </c>
       <c r="F9" s="10" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$C$9:$G$9,1/(1+$B9)^DCF!$C$10:$G$10)+DCF!$G$9*(1+F$5)/($B9-F$5)/(1+$B9)^DCF!$G$10)*1000/DCF!$C$22</f>
-        <v>63058.8421610826</v>
+        <v>66436.6127064959</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2373,19 +2572,19 @@
       </c>
       <c r="C10" s="10" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$C$9:$G$9,1/(1+$B10)^DCF!$C$10:$G$10)+DCF!$G$9*(1+C$5)/($B10-C$5)/(1+$B10)^DCF!$G$10)*1000/DCF!$C$22</f>
-        <v>52120.8432849482</v>
+        <v>55036.2541401443</v>
       </c>
       <c r="D10" s="10" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$C$9:$G$9,1/(1+$B10)^DCF!$C$10:$G$10)+DCF!$G$9*(1+D$5)/($B10-D$5)/(1+$B10)^DCF!$G$10)*1000/DCF!$C$22</f>
-        <v>54187.3910263047</v>
+        <v>57218.3954778092</v>
       </c>
       <c r="E10" s="10" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$C$9:$G$9,1/(1+$B10)^DCF!$C$10:$G$10)+DCF!$G$9*(1+E$5)/($B10-E$5)/(1+$B10)^DCF!$G$10)*1000/DCF!$C$22</f>
-        <v>56497.0620313503</v>
+        <v>59657.2593257877</v>
       </c>
       <c r="F10" s="10" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$C$9:$G$9,1/(1+$B10)^DCF!$C$10:$G$10)+DCF!$G$9*(1+F$5)/($B10-F$5)/(1+$B10)^DCF!$G$10)*1000/DCF!$C$22</f>
-        <v>59095.4419120266</v>
+        <v>62400.9811547635</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2394,19 +2593,19 @@
       </c>
       <c r="C11" s="10" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$C$9:$G$9,1/(1+$B11)^DCF!$C$10:$G$10)+DCF!$G$9*(1+C$5)/($B11-C$5)/(1+$B11)^DCF!$G$10)*1000/DCF!$C$22</f>
-        <v>49473.1411778753</v>
+        <v>52357.4512535389</v>
       </c>
       <c r="D11" s="10" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$C$9:$G$9,1/(1+$B11)^DCF!$C$10:$G$10)+DCF!$G$9*(1+D$5)/($B11-D$5)/(1+$B11)^DCF!$G$10)*1000/DCF!$C$22</f>
-        <v>51300.0435137957</v>
+        <v>54290.8629537182</v>
       </c>
       <c r="E11" s="10" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$C$9:$G$9,1/(1+$B11)^DCF!$C$10:$G$10)+DCF!$G$9*(1+E$5)/($B11-E$5)/(1+$B11)^DCF!$G$10)*1000/DCF!$C$22</f>
-        <v>53329.9349981517</v>
+        <v>56439.0981761397</v>
       </c>
       <c r="F11" s="10" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$C$9:$G$9,1/(1+$B11)^DCF!$C$10:$G$10)+DCF!$G$9*(1+F$5)/($B11-F$5)/(1+$B11)^DCF!$G$10)*1000/DCF!$C$22</f>
-        <v>55598.6372453732</v>
+        <v>58840.0669541403</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2415,24 +2614,24 @@
       </c>
       <c r="C12" s="10" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$C$9:$G$9,1/(1+$B12)^DCF!$C$10:$G$10)+DCF!$G$9*(1+C$5)/($B12-C$5)/(1+$B12)^DCF!$G$10)*1000/DCF!$C$22</f>
-        <v>47078.249884581</v>
+        <v>49934.0246096731</v>
       </c>
       <c r="D12" s="10" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$C$9:$G$9,1/(1+$B12)^DCF!$C$10:$G$10)+DCF!$G$9*(1+D$5)/($B12-D$5)/(1+$B12)^DCF!$G$10)*1000/DCF!$C$22</f>
-        <v>48701.9717469059</v>
+        <v>51656.2417190892</v>
       </c>
       <c r="E12" s="10" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$C$9:$G$9,1/(1+$B12)^DCF!$C$10:$G$10)+DCF!$G$9*(1+E$5)/($B12-E$5)/(1+$B12)^DCF!$G$10)*1000/DCF!$C$22</f>
-        <v>50496.6117000019</v>
+        <v>53559.7448400229</v>
       </c>
       <c r="F12" s="10" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$C$9:$G$9,1/(1+$B12)^DCF!$C$10:$G$10)+DCF!$G$9*(1+F$5)/($B12-F$5)/(1+$B12)^DCF!$G$10)*1000/DCF!$C$22</f>
-        <v>52490.6560923306</v>
+        <v>55674.748307727</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="23" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="C14" s="23"/>
       <c r="D14" s="23"/>
@@ -2469,84 +2668,84 @@
   <sheetData>
     <row r="2" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="3" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="24" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="C5" s="24" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="D5" s="24" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="E5" s="24" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="5" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="D6" s="27" t="n">
+        <v>74</v>
+      </c>
+      <c r="D6" s="28" t="n">
         <f aca="false">Assumptions!E10/Assumptions!E7</f>
         <v>4.88276161528441</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="5" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="D7" s="28" t="n">
+        <v>77</v>
+      </c>
+      <c r="D7" s="29" t="n">
         <v>4.9</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="4" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="29" t="s">
-        <v>74</v>
-      </c>
-      <c r="C10" s="29"/>
-      <c r="D10" s="29"/>
-      <c r="E10" s="29"/>
-      <c r="F10" s="29"/>
+      <c r="B10" s="30" t="s">
+        <v>80</v>
+      </c>
+      <c r="C10" s="30"/>
+      <c r="D10" s="30"/>
+      <c r="E10" s="30"/>
+      <c r="F10" s="30"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="29"/>
-      <c r="C11" s="29"/>
-      <c r="D11" s="29"/>
-      <c r="E11" s="29"/>
-      <c r="F11" s="29"/>
+      <c r="B11" s="30"/>
+      <c r="C11" s="30"/>
+      <c r="D11" s="30"/>
+      <c r="E11" s="30"/>
+      <c r="F11" s="30"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="29"/>
-      <c r="C12" s="29"/>
-      <c r="D12" s="29"/>
-      <c r="E12" s="29"/>
-      <c r="F12" s="29"/>
+      <c r="B12" s="30"/>
+      <c r="C12" s="30"/>
+      <c r="D12" s="30"/>
+      <c r="E12" s="30"/>
+      <c r="F12" s="30"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2575,21 +2774,21 @@
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="30" t="s">
-        <v>75</v>
+      <c r="B2" s="31" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="4" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="31" t="s">
-        <v>78</v>
+      <c r="B6" s="32" t="s">
+        <v>84</v>
       </c>
       <c r="D6" s="4" t="str">
         <f aca="false">IF(Assumptions!E24&lt;Assumptions!E23,"OK","A VERIFIER")</f>
@@ -2597,8 +2796,8 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="31" t="s">
-        <v>79</v>
+      <c r="B7" s="32" t="s">
+        <v>85</v>
       </c>
       <c r="D7" s="4" t="str">
         <f aca="false">IF(MIN(Assumptions!C20:G20)&gt;0,"OK","A VERIFIER")</f>
@@ -2606,8 +2805,8 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="31" t="s">
-        <v>80</v>
+      <c r="B8" s="32" t="s">
+        <v>86</v>
       </c>
       <c r="D8" s="4" t="str">
         <f aca="false">IF(ROUND(DCF!C14+DCF!C17-DCF!C19,1)=0,"OK","A VERIFIER")</f>
@@ -2615,8 +2814,8 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="31" t="s">
-        <v>81</v>
+      <c r="B9" s="32" t="s">
+        <v>87</v>
       </c>
       <c r="D9" s="4" t="str">
         <f aca="false">IF(ROUND(Assumptions!E10*1000/Assumptions!E9-Assumptions!E15,0)=0,"OK","A VERIFIER")</f>
@@ -2624,8 +2823,8 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="31" t="s">
-        <v>82</v>
+      <c r="B10" s="32" t="s">
+        <v>88</v>
       </c>
       <c r="D10" s="4" t="str">
         <f aca="false">IF(DCF!C19&gt;0,"OK","A VERIFIER")</f>
@@ -2634,32 +2833,41 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="4" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="C12" s="4" t="str">
-        <f aca="false">IF(COUNTIF(D6:D10,"OK")=5,"Tous les contrôles sont OK","Au moins un contrôle à vérifier")</f>
+        <f aca="false">IF(COUNTIF(D6:D13,"OK")=6,"Tous les contrôles sont OK","Au moins un contrôle à vérifier")</f>
         <v>Tous les contrôles sont OK</v>
       </c>
     </row>
+    <row r="13" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B13" s="32" t="s">
+        <v>90</v>
+      </c>
+      <c r="D13" s="4" t="str">
+        <f aca="false">IF(AND(DCF!C35&gt;=0.5*DCF!C36,DCF!C35&lt;=2*DCF!C36),"OK","A VERIFIER")</f>
+        <v>OK</v>
+      </c>
+    </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="32" t="s">
-        <v>84</v>
-      </c>
-      <c r="C15" s="32"/>
-      <c r="D15" s="32"/>
-      <c r="E15" s="32"/>
+      <c r="B15" s="33" t="s">
+        <v>91</v>
+      </c>
+      <c r="C15" s="33"/>
+      <c r="D15" s="33"/>
+      <c r="E15" s="33"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="32"/>
-      <c r="C16" s="32"/>
-      <c r="D16" s="32"/>
-      <c r="E16" s="32"/>
+      <c r="B16" s="33"/>
+      <c r="C16" s="33"/>
+      <c r="D16" s="33"/>
+      <c r="E16" s="33"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="32"/>
-      <c r="C17" s="32"/>
-      <c r="D17" s="32"/>
-      <c r="E17" s="32"/>
+      <c r="B17" s="33"/>
+      <c r="C17" s="33"/>
+      <c r="D17" s="33"/>
+      <c r="E17" s="33"/>
     </row>
   </sheetData>
   <mergeCells count="1">
